--- a/weel4dashboard.xlsx
+++ b/weel4dashboard.xlsx
@@ -27,14 +27,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
   <si>
     <t>Tea Shop 3-Year Financial Dashboard</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>3-Year Total Profit</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>Month2</t>
@@ -149,13 +149,53 @@
   </si>
   <si>
     <t>Month1</t>
+  </si>
+  <si>
+    <t>情景</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>单价</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>销量</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>总销售额</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>基准情景</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1000/1500/2500/1000/1000</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>乐观情景</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2000/3000/3500/4000/2000</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>悲观情景</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>500/750/400/800/500</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -165,9 +205,26 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="9"/>
       <name val="等线"/>
       <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -207,21 +264,62 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0070C0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -230,24 +328,42 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -311,72 +427,19 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="zh-CN" altLang="en-US"/>
-              <a:t>累计利润</a:t>
-            </a:r>
-            <a:endParaRPr lang="en-US" altLang="zh-CN"/>
-          </a:p>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:endParaRPr lang="en-US" altLang="zh-CN"/>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:layout/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="zh-CN"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
+    <c:autoTitleDeleted val="1"/>
     <c:plotArea>
-      <c:layout/>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.1506054390260041"/>
+          <c:y val="3.3003300330033E-2"/>
+          <c:w val="0.80454630671166105"/>
+          <c:h val="0.66849094358254724"/>
+        </c:manualLayout>
+      </c:layout>
       <c:lineChart>
         <c:grouping val="standard"/>
         <c:varyColors val="0"/>
@@ -728,7 +791,7 @@
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
+                <a:latin typeface="Segoe UI Emoji" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
                 <a:ea typeface="+mn-ea"/>
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
@@ -787,7 +850,7 @@
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
+                <a:latin typeface="Segoe UI Emoji" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
                 <a:ea typeface="+mn-ea"/>
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
@@ -802,6 +865,645 @@
       <c:spPr>
         <a:noFill/>
         <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="zh-CN"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-CN"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Lower Price Drives Higher Demand</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-CN"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="4.5627997334659748E-2"/>
+          <c:y val="0.19631760644418872"/>
+          <c:w val="0.92489246353145083"/>
+          <c:h val="0.71853368731670342"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Demand Curve for milk tea</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:marker>
+              <c:symbol val="circle"/>
+              <c:size val="5"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:ln w="9525">
+                  <a:solidFill>
+                    <a:schemeClr val="accent1"/>
+                  </a:solidFill>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:marker>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:ln w="28575" cap="rnd">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-B199-464C-8B1B-5DB9C67F657A}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:marker>
+              <c:symbol val="circle"/>
+              <c:size val="5"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:ln w="9525">
+                  <a:solidFill>
+                    <a:schemeClr val="accent1"/>
+                  </a:solidFill>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:marker>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:ln w="28575" cap="rnd">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-B199-464C-8B1B-5DB9C67F657A}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:marker>
+              <c:symbol val="circle"/>
+              <c:size val="5"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:ln w="9525">
+                  <a:solidFill>
+                    <a:schemeClr val="accent1"/>
+                  </a:solidFill>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:marker>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:ln w="28575" cap="rnd">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-B199-464C-8B1B-5DB9C67F657A}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="5"/>
+            <c:marker>
+              <c:symbol val="circle"/>
+              <c:size val="5"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:ln w="9525">
+                  <a:solidFill>
+                    <a:schemeClr val="accent1"/>
+                  </a:solidFill>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:marker>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-B199-464C-8B1B-5DB9C67F657A}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="6"/>
+            <c:marker>
+              <c:symbol val="circle"/>
+              <c:size val="5"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:ln w="9525">
+                  <a:solidFill>
+                    <a:schemeClr val="accent1"/>
+                  </a:solidFill>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:marker>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:ln w="28575" cap="rnd">
+                <a:solidFill>
+                  <a:srgbClr val="0070C0"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000009-B199-464C-8B1B-5DB9C67F657A}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="7"/>
+            <c:marker>
+              <c:symbol val="circle"/>
+              <c:size val="5"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:ln w="9525">
+                  <a:solidFill>
+                    <a:schemeClr val="accent1"/>
+                  </a:solidFill>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:marker>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:ln w="28575" cap="rnd">
+                <a:solidFill>
+                  <a:srgbClr val="0070C0"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000B-B199-464C-8B1B-5DB9C67F657A}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="8"/>
+            <c:marker>
+              <c:symbol val="circle"/>
+              <c:size val="5"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:ln w="9525">
+                  <a:solidFill>
+                    <a:schemeClr val="accent1"/>
+                  </a:solidFill>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:marker>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:ln w="28575" cap="rnd">
+                <a:solidFill>
+                  <a:srgbClr val="0070C0"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000D-B199-464C-8B1B-5DB9C67F657A}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="9"/>
+            <c:marker>
+              <c:symbol val="circle"/>
+              <c:size val="5"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:ln w="9525">
+                  <a:solidFill>
+                    <a:schemeClr val="accent1"/>
+                  </a:solidFill>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:marker>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:ln w="28575" cap="rnd">
+                <a:solidFill>
+                  <a:srgbClr val="0070C0"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000F-B199-464C-8B1B-5DB9C67F657A}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:xVal>
+            <c:numRef>
+              <c:f>[1]Demand_Curve!$B$2:$B$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>250</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>300</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>350</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>400</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>550</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>[1]Demand_Curve!$A$2:$A$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>6</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000010-B199-464C-8B1B-5DB9C67F657A}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="415067312"/>
+        <c:axId val="415067968"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="415067312"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="415067968"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="415067968"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="415067312"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="25400">
           <a:noFill/>
         </a:ln>
         <a:effectLst/>
@@ -841,6 +1543,7 @@
     <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
     <c:pageSetup/>
   </c:printSettings>
+  <c:userShapes r:id="rId3"/>
 </c:chartSpace>
 </file>
 
@@ -884,6 +1587,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
   <cs:axisTitle>
@@ -1387,20 +2130,536 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>601980</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>60960</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>441960</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>571500</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>91440</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>411480</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>83820</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -1421,7 +2680,146 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>464820</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>15240</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>464820</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="图表 2"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:userShapes xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
+    <cdr:from>
+      <cdr:x>0.22333</cdr:x>
+      <cdr:y>0.11528</cdr:y>
+    </cdr:from>
+    <cdr:to>
+      <cdr:x>0.39333</cdr:x>
+      <cdr:y>0.19861</cdr:y>
+    </cdr:to>
+    <cdr:sp macro="" textlink="">
+      <cdr:nvSpPr>
+        <cdr:cNvPr id="4" name="文本框 3"/>
+        <cdr:cNvSpPr txBox="1"/>
+      </cdr:nvSpPr>
+      <cdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="1021080" y="316230"/>
+          <a:ext cx="777240" cy="228600"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </cdr:spPr>
+      <cdr:txBody>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" vertOverflow="clip" wrap="none" rtlCol="0"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+        </a:p>
+      </cdr:txBody>
+    </cdr:sp>
+  </cdr:relSizeAnchor>
+  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
+    <cdr:from>
+      <cdr:x>0.23</cdr:x>
+      <cdr:y>0.12639</cdr:y>
+    </cdr:from>
+    <cdr:to>
+      <cdr:x>0.37333</cdr:x>
+      <cdr:y>0.19583</cdr:y>
+    </cdr:to>
+    <cdr:sp macro="" textlink="">
+      <cdr:nvSpPr>
+        <cdr:cNvPr id="5" name="文本框 4"/>
+        <cdr:cNvSpPr txBox="1"/>
+      </cdr:nvSpPr>
+      <cdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="1051560" y="346710"/>
+          <a:ext cx="655320" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </cdr:spPr>
+      <cdr:txBody>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" vertOverflow="clip" wrap="none" rtlCol="0"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+        </a:p>
+      </cdr:txBody>
+    </cdr:sp>
+  </cdr:relSizeAnchor>
+  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
+    <cdr:from>
+      <cdr:x>0.21167</cdr:x>
+      <cdr:y>0.15139</cdr:y>
+    </cdr:from>
+    <cdr:to>
+      <cdr:x>0.42667</cdr:x>
+      <cdr:y>0.24306</cdr:y>
+    </cdr:to>
+    <cdr:sp macro="" textlink="">
+      <cdr:nvSpPr>
+        <cdr:cNvPr id="6" name="文本框 5"/>
+        <cdr:cNvSpPr txBox="1"/>
+      </cdr:nvSpPr>
+      <cdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="967740" y="415290"/>
+          <a:ext cx="982980" cy="251460"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </cdr:spPr>
+      <cdr:txBody>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" vertOverflow="clip" wrap="none" rtlCol="0"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100"/>
+            <a:t>Elasitc (PED&gt;1)</a:t>
+          </a:r>
+        </a:p>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+        </a:p>
+      </cdr:txBody>
+    </cdr:sp>
+  </cdr:relSizeAnchor>
+</c:userShapes>
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1729,7 +3127,88 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2"/>
+      <sheetData sheetId="2">
+        <row r="2">
+          <cell r="A2">
+            <v>15</v>
+          </cell>
+          <cell r="B2">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="A3">
+            <v>14</v>
+          </cell>
+          <cell r="B3">
+            <v>150</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="A4">
+            <v>13</v>
+          </cell>
+          <cell r="B4">
+            <v>200</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="A5">
+            <v>12</v>
+          </cell>
+          <cell r="B5">
+            <v>250</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="A6">
+            <v>11</v>
+          </cell>
+          <cell r="B6">
+            <v>300</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="A7">
+            <v>10</v>
+          </cell>
+          <cell r="B7">
+            <v>350</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="A8">
+            <v>9</v>
+          </cell>
+          <cell r="B8">
+            <v>400</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="A9">
+            <v>8</v>
+          </cell>
+          <cell r="B9">
+            <v>450</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="A10">
+            <v>7</v>
+          </cell>
+          <cell r="B10">
+            <v>500</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="A11">
+            <v>6</v>
+          </cell>
+          <cell r="B11">
+            <v>550</v>
+          </cell>
+        </row>
+      </sheetData>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -2000,6 +3479,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J44"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="6" max="6" width="13.21875" customWidth="1"/>
+    <col min="7" max="7" width="14.6640625" customWidth="1"/>
+    <col min="8" max="8" width="19.44140625" customWidth="1"/>
+    <col min="9" max="9" width="12.88671875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
@@ -2119,7 +3604,7 @@
         <v>80000</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>9</v>
       </c>
@@ -2127,7 +3612,7 @@
         <v>90000</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>10</v>
       </c>
@@ -2135,7 +3620,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>11</v>
       </c>
@@ -2143,7 +3628,7 @@
         <v>110000</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>12</v>
       </c>
@@ -2151,7 +3636,7 @@
         <v>120000</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>13</v>
       </c>
@@ -2159,7 +3644,7 @@
         <v>122500</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>14</v>
       </c>
@@ -2167,7 +3652,7 @@
         <v>125000</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>15</v>
       </c>
@@ -2175,7 +3660,7 @@
         <v>127500</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>16</v>
       </c>
@@ -2183,7 +3668,7 @@
         <v>130000</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>17</v>
       </c>
@@ -2191,7 +3676,7 @@
         <v>132500</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>18</v>
       </c>
@@ -2199,7 +3684,7 @@
         <v>135000</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>19</v>
       </c>
@@ -2207,7 +3692,7 @@
         <v>137500</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>20</v>
       </c>
@@ -2215,36 +3700,84 @@
         <v>140000</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>21</v>
       </c>
       <c r="B29">
         <v>142500</v>
       </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="F29" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="G29" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="H29" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="I29" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>22</v>
       </c>
       <c r="B30">
         <v>145000</v>
       </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="F30" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="G30" s="8">
+        <v>20</v>
+      </c>
+      <c r="H30" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="I30" s="9">
+        <v>140000</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>23</v>
       </c>
       <c r="B31">
         <v>147500</v>
       </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="F31" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="G31" s="8">
+        <v>25</v>
+      </c>
+      <c r="H31" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="I31" s="9">
+        <v>362500</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>24</v>
       </c>
       <c r="B32">
         <v>150000</v>
+      </c>
+      <c r="F32" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="G32" s="8">
+        <v>10</v>
+      </c>
+      <c r="H32" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="I32" s="9">
+        <v>29500</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
@@ -2349,7 +3882,7 @@
     <mergeCell ref="A4:C5"/>
     <mergeCell ref="A6:C6"/>
   </mergeCells>
-  <phoneticPr fontId="1" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="A4">
     <cfRule type="dataBar" priority="2">
       <dataBar>
@@ -2379,7 +3912,8 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
